--- a/daily_matches/job_matches_2026-04-05.xlsx
+++ b/daily_matches/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist (Applied AI Scientist) - Innovation Lab</t>
+          <t>Senior Software Engineer - Basking Ridge, NJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,104 +486,104 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, CI/CD, Python</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Kafka, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4302abc692fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8d86e637a87630</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Polars, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089f39014e9515e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Software Engineer III- Python / Numpy / Pandas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd96f5b78abfcf</t>
+          <t>https://www.indeed.com/viewjob?jk=36ae5d9bdff33f02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CCB Risk Program Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hasbro, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, Snowflake, Databricks, Redshift, Kafka, Python, SQL, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, Git, Hadoop, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,147 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c4391cd5e19893</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Tester</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ace46cc419bb3bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Newtown Square, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Digital Supply Chain Summer/Fall Co-Op</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9698d8e2445e3e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Software Engineer – AI Core Team</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DTN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=455f6256d9470cef</t>
+          <t>https://www.indeed.com/viewjob?jk=248e7ec87211dd21</t>
         </is>
       </c>
     </row>
